--- a/output/2026-10-11_05_Serbia_Sumadijski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-11_05_Serbia_Sumadijski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Woby Haus - prodaja masina i alata</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -490,10 +489,9 @@
           <t>034/356-722</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Negozio generalista di macchine e utensili, catena con piu filiali in Serbia. Sito ufficiale non reperito; esistenza confermata su directory planplus.rs.</t>
+          <t>Negozio generalista di macchine e utensili, catena con piu filiali in Serbia. Sito ufficiale non reperito; esistenza confermata su directory planplus.rs. [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +506,6 @@
           <t>Roanda Komerc - STIHL prodaja i servis</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -524,10 +521,9 @@
           <t>034/251-708</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore/servizio autorizzato STIHL (power tools/giardinaggio). ATTENZIONE: fonti discordanti sull'indirizzo (Svetozara Markovica 29 vs Kneza Mihaila 155A) - verificare prima del contatto. Fit settoriale moderato.</t>
+          <t>Rivenditore/servizio autorizzato STIHL (power tools/giardinaggio). ATTENZIONE: fonti discordanti sull'indirizzo (Svetozara Markovica 29 vs Kneza Mihaila 155A) - verificare prima del contatto. Fit settoriale moderato. [DUPLICATO — vedi anche: 2026-10-11_00_Serbia_Braničevski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -542,7 +538,6 @@
           <t>Tempo Tehnika Kragujevac</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -553,8 +548,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Rivenditore utensili elettrici Stanley/DeWalt, confermato tramite listing prodotti su eponuda.com. Possibile negozio misto elettrodomestici/utensili. Discrepanza civico (13 vs 17) tra fonti.</t>
@@ -614,7 +607,6 @@
           <t>Wurth Pick &amp; Go Kragujevac</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -630,7 +622,6 @@
           <t>034/301-880</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Punto vendita Würth B2B multibrand (utensili, PPE, saldatura), confermato su piu listing directory. Buon fit: serve clienti business con condizioni all'ingrosso.</t>
@@ -648,7 +639,6 @@
           <t>Delmax - sve za auto</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Arandjelovac</t>
@@ -664,10 +654,9 @@
           <t>034/617-0200</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Importatore/distributore di attrezzature per officine auto. Esistenza confermata su directory; elenco marchi trattati (Würth/Bosch/Jonnesway/Comec/Usag) da fonte generica di categoria, non specifica all'azienda - da verificare direttamente. Sito delmax.rs citato da fonte terza con dati anagrafici incoerenti, non considerato verificato.</t>
+          <t>Importatore/distributore di attrezzature per officine auto. Esistenza confermata su directory; elenco marchi trattati (Würth/Bosch/Jonnesway/Comec/Usag) da fonte generica di categoria, non specifica all'azienda - da verificare direttamente. Sito delmax.rs citato da fonte terza con dati anagrafici incoerenti, non considerato verificato. [DUPLICATO — vedi anche: 2026-10-11_00_Serbia_Braničevski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -682,7 +671,6 @@
           <t>Autostart Shop</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -698,7 +686,6 @@
           <t>034/632-5007</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Attrezzature professionali per autofficine, stessa categoria di Delmax. Esistenza confermata su directory planplus.rs.</t>
@@ -716,7 +703,6 @@
           <t>Sumadija Trans Prom - STIHL prodaja i servis</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Arandjelovac</t>
@@ -732,7 +718,6 @@
           <t>034/720-780</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Rivenditore/servizio autorizzato STIHL (power tools/giardinaggio). Nessun sito ufficiale reperito. Fit settoriale moderato.</t>
@@ -750,7 +735,6 @@
           <t>Plecevic - STIHL prodaja i servis</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Topola</t>
@@ -766,7 +750,6 @@
           <t>034/681-4995</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Rivenditore multibrand power tools/giardinaggio (STIHL, Villager, AGM, Black&amp;Decker, DeWalt, Gardena). Esistenza confermata su directory.</t>
@@ -784,7 +767,6 @@
           <t>Sloga d.o.o.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Kragujevac</t>
@@ -795,8 +777,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Trader/rivenditore di macchine per lavorazione metalli (machine tools usate), categorizzato come 'Trgovac' (dealer) su profilo Machineseeker. Nessun sito/telefono/email proprio reperito.</t>
